--- a/APP/static/archivos/Plantilla Referencia Empresas.xlsx
+++ b/APP/static/archivos/Plantilla Referencia Empresas.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>USUARIO</t>
   </si>
@@ -20,9 +20,6 @@
   </si>
   <si>
     <t>EMAIL</t>
-  </si>
-  <si>
-    <t>TIPO_PERFIL</t>
   </si>
   <si>
     <t>NOMBRE</t>
@@ -65,15 +62,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -157,13 +151,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E2" displayName="Tabla" name="Tabla" id="1">
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D2" displayName="Tabla" name="Tabla" id="1">
+  <tableColumns count="4">
     <tableColumn name="USUARIO" id="1"/>
     <tableColumn name="CONTRASEÑA" id="2"/>
     <tableColumn name="EMAIL" id="3"/>
-    <tableColumn name="TIPO_PERFIL" id="4"/>
-    <tableColumn name="NOMBRE" id="5"/>
+    <tableColumn name="NOMBRE" id="4"/>
   </tableColumns>
   <tableStyleInfo name="CARGA EMPRESA-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -370,7 +363,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="5" width="25.13"/>
+    <col customWidth="1" min="1" max="4" width="25.13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -386,23 +379,14 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2">
-      <formula1>"EMPRESA"</formula1>
-    </dataValidation>
-  </dataValidations>
   <drawing r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
